--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_22sep26_Tue.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_22sep26_Tue.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3431" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3430" uniqueCount="310">
   <si>
     <t>Date</t>
   </si>
@@ -1126,7 +1126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1300,6 +1300,27 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1700,7 +1721,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B2, $C$2:$C$718, C2, $D$2:$D$718, D2, $E$2:$E$718, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$718, B2, $C$2:$C$718, C2, $D$2:$D$718, D2, $E$2:$E$718, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -1739,7 +1760,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B3, $C$2:$C$718, C3, $D$2:$D$718, D3, $E$2:$E$718, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1778,7 +1799,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B4, $C$2:$C$718, C4, $D$2:$D$718, D4, $E$2:$E$718, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1824,7 +1845,7 @@
         <v>10880</v>
       </c>
       <c r="N5" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B5, $C$2:$C$718, C5, $D$2:$D$718, D5, $E$2:$E$718, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -1865,7 +1886,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B6, $C$2:$C$718, C6, $D$2:$D$718, D6, $E$2:$E$718, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1902,7 +1923,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B7, $C$2:$C$718, C7, $D$2:$D$718, D7, $E$2:$E$718, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1941,7 +1962,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B8, $C$2:$C$718, C8, $D$2:$D$718, D8, $E$2:$E$718, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1987,7 +2008,7 @@
         <v>10680</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B9, $C$2:$C$718, C9, $D$2:$D$718, D9, $E$2:$E$718, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
@@ -2026,7 +2047,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B10, $C$2:$C$718, C10, $D$2:$D$718, D10, $E$2:$E$718, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2065,7 +2086,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B11, $C$2:$C$718, C11, $D$2:$D$718, D11, $E$2:$E$718, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2102,7 +2123,7 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B12, $C$2:$C$718, C12, $D$2:$D$718, D12, $E$2:$E$718, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2141,7 +2162,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B13, $C$2:$C$718, C13, $D$2:$D$718, D13, $E$2:$E$718, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2178,7 +2199,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B14, $C$2:$C$718, C14, $D$2:$D$718, D14, $E$2:$E$718, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2215,7 +2236,7 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B15, $C$2:$C$718, C15, $D$2:$D$718, D15, $E$2:$E$718, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2254,7 +2275,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B16, $C$2:$C$718, C16, $D$2:$D$718, D16, $E$2:$E$718, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2291,7 +2312,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B17, $C$2:$C$718, C17, $D$2:$D$718, D17, $E$2:$E$718, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2337,7 +2358,7 @@
         <v>302</v>
       </c>
       <c r="N18" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B18, $C$2:$C$718, C18, $D$2:$D$718, D18, $E$2:$E$718, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="10"/>
@@ -2380,7 +2401,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B19, $C$2:$C$718, C19, $D$2:$D$718, D19, $E$2:$E$718, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2417,7 +2438,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B20, $C$2:$C$718, C20, $D$2:$D$718, D20, $E$2:$E$718, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20"/>
@@ -2465,7 +2486,7 @@
         <v>314</v>
       </c>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B21, $C$2:$C$718, C21, $D$2:$D$718, D21, $E$2:$E$718, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2502,7 +2523,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B22, $C$2:$C$718, C22, $D$2:$D$718, D22, $E$2:$E$718, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22"/>
@@ -2541,7 +2562,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B23, $C$2:$C$718, C23, $D$2:$D$718, D23, $E$2:$E$718, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23"/>
@@ -2580,7 +2601,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B24, $C$2:$C$718, C24, $D$2:$D$718, D24, $E$2:$E$718, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -2629,7 +2650,7 @@
         <v>540</v>
       </c>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B25, $C$2:$C$718, C25, $D$2:$D$718, D25, $E$2:$E$718, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25"/>
@@ -2677,7 +2698,7 @@
         <v>300</v>
       </c>
       <c r="N26" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B26, $C$2:$C$718, C26, $D$2:$D$718, D26, $E$2:$E$718, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26"/>
@@ -2718,7 +2739,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B27, $C$2:$C$718, C27, $D$2:$D$718, D27, $E$2:$E$718, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27"/>
@@ -2759,7 +2780,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B28, $C$2:$C$718, C28, $D$2:$D$718, D28, $E$2:$E$718, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
@@ -2798,7 +2819,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B29, $C$2:$C$718, C29, $D$2:$D$718, D29, $E$2:$E$718, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29"/>
@@ -2839,7 +2860,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B30, $C$2:$C$718, C30, $D$2:$D$718, D30, $E$2:$E$718, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30"/>
@@ -2878,7 +2899,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B31, $C$2:$C$718, C31, $D$2:$D$718, D31, $E$2:$E$718, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -2917,7 +2938,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B32, $C$2:$C$718, C32, $D$2:$D$718, D32, $E$2:$E$718, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
@@ -2958,7 +2979,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B33, $C$2:$C$718, C33, $D$2:$D$718, D33, $E$2:$E$718, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -2997,7 +3018,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B34, $C$2:$C$718, C34, $D$2:$D$718, D34, $E$2:$E$718, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -3038,7 +3059,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B35, $C$2:$C$718, C35, $D$2:$D$718, D35, $E$2:$E$718, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35"/>
@@ -3078,7 +3099,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B36, $C$2:$C$718, C36, $D$2:$D$718, D36, $E$2:$E$718, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P36"/>
@@ -3119,7 +3140,7 @@
         <v>3156</v>
       </c>
       <c r="N37" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B37, $C$2:$C$718, C37, $D$2:$D$718, D37, $E$2:$E$718, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P37" s="19"/>
@@ -3159,7 +3180,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B38, $C$2:$C$718, C38, $D$2:$D$718, D38, $E$2:$E$718, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
@@ -3198,7 +3219,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B39, $C$2:$C$718, C39, $D$2:$D$718, D39, $E$2:$E$718, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39"/>
@@ -3237,7 +3258,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B40, $C$2:$C$718, C40, $D$2:$D$718, D40, $E$2:$E$718, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40"/>
@@ -3285,7 +3306,7 @@
         <v>225</v>
       </c>
       <c r="N41" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B41, $C$2:$C$718, C41, $D$2:$D$718, D41, $E$2:$E$718, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3331,7 +3352,7 @@
         <v>650</v>
       </c>
       <c r="N42" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B42, $C$2:$C$718, C42, $D$2:$D$718, D42, $E$2:$E$718, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3377,7 +3398,7 @@
         <v>525</v>
       </c>
       <c r="N43" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B43, $C$2:$C$718, C43, $D$2:$D$718, D43, $E$2:$E$718, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3414,7 +3435,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B44, $C$2:$C$718, C44, $D$2:$D$718, D44, $E$2:$E$718, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -3462,7 +3483,7 @@
         <v>300</v>
       </c>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B45, $C$2:$C$718, C45, $D$2:$D$718, D45, $E$2:$E$718, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45" s="10"/>
@@ -3503,7 +3524,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B46, $C$2:$C$718, C46, $D$2:$D$718, D46, $E$2:$E$718, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -3544,7 +3565,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B47, $C$2:$C$718, C47, $D$2:$D$718, D47, $E$2:$E$718, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3590,7 +3611,7 @@
         <v>300</v>
       </c>
       <c r="N48" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B48, $C$2:$C$718, C48, $D$2:$D$718, D48, $E$2:$E$718, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48" s="10"/>
@@ -3637,7 +3658,7 @@
         <v>516</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B49, $C$2:$C$718, C49, $D$2:$D$718, D49, $E$2:$E$718, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3676,7 +3697,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B50, $C$2:$C$718, C50, $D$2:$D$718, D50, $E$2:$E$718, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -3717,7 +3738,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B51, $C$2:$C$718, C51, $D$2:$D$718, D51, $E$2:$E$718, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -3766,7 +3787,7 @@
         <v>175</v>
       </c>
       <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B52, $C$2:$C$718, C52, $D$2:$D$718, D52, $E$2:$E$718, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3805,7 +3826,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B53, $C$2:$C$718, C53, $D$2:$D$718, D53, $E$2:$E$718, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
@@ -3846,7 +3867,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B54, $C$2:$C$718, C54, $D$2:$D$718, D54, $E$2:$E$718, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -3894,7 +3915,7 @@
         <v>650</v>
       </c>
       <c r="N55" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B55, $C$2:$C$718, C55, $D$2:$D$718, D55, $E$2:$E$718, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3933,7 +3954,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B56, $C$2:$C$718, C56, $D$2:$D$718, D56, $E$2:$E$718, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56" s="10"/>
@@ -3981,7 +4002,7 @@
         <v>500</v>
       </c>
       <c r="N57" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B57, $C$2:$C$718, C57, $D$2:$D$718, D57, $E$2:$E$718, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57" s="10"/>
@@ -4020,7 +4041,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B58, $C$2:$C$718, C58, $D$2:$D$718, D58, $E$2:$E$718, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -4060,7 +4081,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B59, $C$2:$C$718, C59, $D$2:$D$718, D59, $E$2:$E$718, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
@@ -4101,7 +4122,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B60, $C$2:$C$718, C60, $D$2:$D$718, D60, $E$2:$E$718, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60" s="10"/>
@@ -4142,7 +4163,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B61, $C$2:$C$718, C61, $D$2:$D$718, D61, $E$2:$E$718, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61" s="30"/>
@@ -4182,7 +4203,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B62, $C$2:$C$718, C62, $D$2:$D$718, D62, $E$2:$E$718, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4228,7 +4249,7 @@
         <v>720</v>
       </c>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B63, $C$2:$C$718, C63, $D$2:$D$718, D63, $E$2:$E$718, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63" s="10"/>
@@ -4267,7 +4288,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B64, $C$2:$C$718, C64, $D$2:$D$718, D64, $E$2:$E$718, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64" s="10"/>
@@ -4315,7 +4336,7 @@
         <v>300</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B65, $C$2:$C$718, C65, $D$2:$D$718, D65, $E$2:$E$718, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O65" s="10"/>
@@ -4363,7 +4384,7 @@
         <v>300</v>
       </c>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B66, $C$2:$C$718, C66, $D$2:$D$718, D66, $E$2:$E$718, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$718, B66, $C$2:$C$718, C66, $D$2:$D$718, D66, $E$2:$E$718, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O66" s="10"/>
@@ -4402,7 +4423,7 @@
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B67, $C$2:$C$718, C67, $D$2:$D$718, D67, $E$2:$E$718, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67" s="10"/>
@@ -4441,7 +4462,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B68, $C$2:$C$718, C68, $D$2:$D$718, D68, $E$2:$E$718, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="19"/>
@@ -4481,7 +4502,7 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B69, $C$2:$C$718, C69, $D$2:$D$718, D69, $E$2:$E$718, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69" s="10"/>
@@ -4520,7 +4541,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B70, $C$2:$C$718, C70, $D$2:$D$718, D70, $E$2:$E$718, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P70" s="10"/>
@@ -4567,7 +4588,7 @@
         <v>34175</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B71, $C$2:$C$718, C71, $D$2:$D$718, D71, $E$2:$E$718, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5240,7 +5261,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="32">
         <v>46281.443055555559</v>
       </c>
@@ -5290,7 +5311,7 @@
       </c>
       <c r="P87" s="31"/>
     </row>
-    <row r="88" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="32">
         <v>46281.388888888891</v>
       </c>
@@ -5340,7 +5361,7 @@
       </c>
       <c r="P88" s="31"/>
     </row>
-    <row r="89" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
         <v>46267.375</v>
       </c>
@@ -5437,7 +5458,7 @@
       <c r="O90" s="10"/>
       <c r="P90" s="10"/>
     </row>
-    <row r="91" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="32">
         <v>46267.425694444442</v>
       </c>
@@ -5487,7 +5508,7 @@
       </c>
       <c r="P91" s="31"/>
     </row>
-    <row r="92" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="32">
         <v>46280.593055555553</v>
       </c>
@@ -5537,7 +5558,7 @@
       </c>
       <c r="P92" s="31"/>
     </row>
-    <row r="93" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="11">
         <v>46273.375</v>
       </c>
@@ -5632,7 +5653,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="43">
         <v>46273.375</v>
       </c>
@@ -5682,7 +5703,7 @@
       </c>
       <c r="P95" s="31"/>
     </row>
-    <row r="96" spans="1:16" s="31" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" s="31" customFormat="1" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="32">
         <v>46274.375</v>
       </c>
@@ -5827,7 +5848,7 @@
       <c r="O98" s="10"/>
       <c r="P98" s="10"/>
     </row>
-    <row r="99" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
         <v>46274.375</v>
       </c>
@@ -5876,7 +5897,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
         <v>46280.375694444447</v>
       </c>
@@ -6099,57 +6120,53 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="52">
+    <row r="105" spans="1:16" s="66" customFormat="1" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="60">
         <v>46262.375</v>
       </c>
-      <c r="B105" s="53" t="s">
+      <c r="B105" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="C105" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="D105" s="54">
+      <c r="C105" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D105" s="62">
         <v>2</v>
       </c>
-      <c r="E105" s="54">
+      <c r="E105" s="62">
         <v>4360</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="62">
         <v>5.3140096620000001</v>
       </c>
-      <c r="G105" s="2" t="s">
+      <c r="G105" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="H105" s="5">
+      <c r="H105" s="64">
         <v>4140</v>
       </c>
-      <c r="I105" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J105" s="47" t="s">
+      <c r="I105" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="J105" s="65" t="s">
         <v>118</v>
       </c>
-      <c r="K105" s="47" t="s">
+      <c r="K105" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="L105" s="47">
+      <c r="L105" s="65">
         <v>8420</v>
       </c>
-      <c r="M105" s="47">
+      <c r="M105" s="65">
         <f>ABS((D105*E105)-L105)</f>
         <v>300</v>
       </c>
-      <c r="N105" s="25" t="str">
+      <c r="N105" s="66" t="str">
         <f>IF(COUNTIFS( $B$2:$B$718, B105, $C$2:$C$718, C105, $D$2:$D$718, D105, $E$2:$E$718, E105) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O105" s="25"/>
-      <c r="P105" s="25" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="106" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
         <v>46269.614583333336</v>
       </c>
@@ -6198,7 +6215,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="11">
         <v>46243.375</v>
       </c>
@@ -6308,7 +6325,7 @@
         <v>5</v>
       </c>
       <c r="E109" s="4">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="F109" s="4">
         <v>5.6279914179999997</v>
@@ -6333,7 +6350,7 @@
       </c>
       <c r="M109" s="18">
         <f>ABS((D109*E109)-L109)</f>
-        <v>300.75</v>
+        <v>275.75</v>
       </c>
       <c r="N109" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$718, B109, $C$2:$C$718, C109, $D$2:$D$718, D109, $E$2:$E$718, E109) &gt; 1, "Duplicate", "Unique")</f>
@@ -6434,48 +6451,48 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="112" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="3">
+    <row r="112" spans="1:16" s="66" customFormat="1" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="60">
         <v>46335.442361111112</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="B112" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D112" s="4">
+      <c r="C112" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" s="62">
         <v>10</v>
       </c>
-      <c r="E112" s="4">
+      <c r="E112" s="62">
         <v>1460</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="62">
         <v>6.0275962239999998</v>
       </c>
-      <c r="G112" s="2" t="s">
+      <c r="G112" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="H112" s="5">
+      <c r="H112" s="64">
         <v>1377</v>
       </c>
-      <c r="I112" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J112" s="18" t="s">
+      <c r="I112" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="J112" s="65" t="s">
         <v>117</v>
       </c>
-      <c r="K112" s="18" t="s">
+      <c r="K112" s="65" t="s">
         <v>270</v>
       </c>
-      <c r="L112" s="18">
+      <c r="L112" s="65">
         <v>14100</v>
       </c>
-      <c r="M112" s="18">
+      <c r="M112" s="65">
         <f>ABS((D112*E112)-L112)</f>
         <v>500</v>
       </c>
-      <c r="N112" s="10" t="str">
+      <c r="N112" s="66" t="str">
         <f>IF(COUNTIFS( $B$2:$B$718, B112, $C$2:$C$718, C112, $D$2:$D$718, D112, $E$2:$E$718, E112) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
@@ -6623,7 +6640,7 @@
       </c>
       <c r="P115"/>
     </row>
-    <row r="116" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -6719,7 +6736,7 @@
       </c>
       <c r="P117" s="19"/>
     </row>
-    <row r="118" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -7033,7 +7050,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -7071,7 +7088,7 @@
       </c>
       <c r="P125"/>
     </row>
-    <row r="126" spans="1:16" s="31" customFormat="1" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16" s="31" customFormat="1" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3">
         <v>46281.375</v>
       </c>
@@ -7349,7 +7366,7 @@
       <c r="O131" s="31"/>
       <c r="P131" s="31"/>
     </row>
-    <row r="132" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3">
         <v>46261.615277777775</v>
       </c>
@@ -7526,7 +7543,7 @@
       </c>
       <c r="O135" s="25"/>
     </row>
-    <row r="136" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -7745,7 +7762,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="141" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -8112,7 +8129,7 @@
       <c r="O148" s="31"/>
       <c r="P148" s="31"/>
     </row>
-    <row r="149" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3">
         <v>46266.375</v>
       </c>
@@ -8161,7 +8178,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="150" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -8476,7 +8493,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="157" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -8576,7 +8593,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="159" spans="1:16" s="31" customFormat="1" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" s="31" customFormat="1" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -8848,7 +8865,7 @@
       <c r="O164"/>
       <c r="P164"/>
     </row>
-    <row r="165" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="3">
         <v>46274.414583333331</v>
       </c>
@@ -9421,7 +9438,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="178" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="32">
         <v>46265.375694444447</v>
       </c>
@@ -9470,7 +9487,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="179" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="43">
         <v>46243.505555555559</v>
       </c>
@@ -9519,7 +9536,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="180" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="32">
         <v>46280.588194444441</v>
       </c>
@@ -10042,7 +10059,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="192" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -10494,7 +10511,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="203" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -10533,7 +10550,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="204" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3">
         <v>46335.421527777777</v>
       </c>
@@ -11318,7 +11335,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="223" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="3">
         <v>46266.375</v>
       </c>
@@ -12163,7 +12180,7 @@
       <c r="I244" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J244" s="18" t="s">
+      <c r="J244" s="56" t="s">
         <v>118</v>
       </c>
       <c r="K244" s="18" t="s">
@@ -12181,7 +12198,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="245" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -21728,8 +21745,11 @@
         <filter val="S"/>
       </filters>
     </filterColumn>
-    <sortState ref="A2:P293">
-      <sortCondition ref="F1"/>
+    <filterColumn colId="14">
+      <filters blank="1"/>
+    </filterColumn>
+    <sortState ref="A72:P293">
+      <sortCondition ref="F1:F293"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
@@ -22098,7 +22118,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B2, $C$2:$C$718, C2, $D$2:$D$718, D2, $E$2:$E$718, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$718, B2, $C$2:$C$718, C2, $D$2:$D$718, D2, $E$2:$E$718, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -22139,7 +22159,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B3, $C$2:$C$718, C3, $D$2:$D$718, D3, $E$2:$E$718, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -22180,7 +22200,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B4, $C$2:$C$718, C4, $D$2:$D$718, D4, $E$2:$E$718, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -22221,7 +22241,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B5, $C$2:$C$718, C5, $D$2:$D$718, D5, $E$2:$E$718, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -22269,7 +22289,7 @@
         <v>34175</v>
       </c>
       <c r="N6" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B6, $C$2:$C$718, C6, $D$2:$D$718, D6, $E$2:$E$718, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -22310,7 +22330,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B7, $C$2:$C$718, C7, $D$2:$D$718, D7, $E$2:$E$718, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22347,7 +22367,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B8, $C$2:$C$718, C8, $D$2:$D$718, D8, $E$2:$E$718, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="26"/>
@@ -22395,7 +22415,7 @@
         <v>300</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B9, $C$2:$C$718, C9, $D$2:$D$718, D9, $E$2:$E$718, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O9" s="10"/>
@@ -22443,7 +22463,7 @@
         <v>300</v>
       </c>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B10, $C$2:$C$718, C10, $D$2:$D$718, D10, $E$2:$E$718, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O10" s="10"/>
@@ -22482,7 +22502,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B11, $C$2:$C$718, C11, $D$2:$D$718, D11, $E$2:$E$718, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="19"/>
@@ -22530,7 +22550,7 @@
         <v>720</v>
       </c>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B12, $C$2:$C$718, C12, $D$2:$D$718, D12, $E$2:$E$718, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
@@ -22569,7 +22589,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B13, $C$2:$C$718, C13, $D$2:$D$718, D13, $E$2:$E$718, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
@@ -22608,7 +22628,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B14, $C$2:$C$718, C14, $D$2:$D$718, D14, $E$2:$E$718, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="10"/>
@@ -22649,7 +22669,7 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B15, $C$2:$C$718, C15, $D$2:$D$718, D15, $E$2:$E$718, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22688,7 +22708,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B16, $C$2:$C$718, C16, $D$2:$D$718, D16, $E$2:$E$718, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="10"/>
@@ -22729,7 +22749,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B17, $C$2:$C$718, C17, $D$2:$D$718, D17, $E$2:$E$718, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="10"/>
@@ -22770,7 +22790,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B18, $C$2:$C$718, C18, $D$2:$D$718, D18, $E$2:$E$718, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="30"/>
@@ -22808,7 +22828,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B19, $C$2:$C$718, C19, $D$2:$D$718, D19, $E$2:$E$718, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22845,7 +22865,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B20, $C$2:$C$718, C20, $D$2:$D$718, D20, $E$2:$E$718, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20"/>
@@ -22892,7 +22912,7 @@
         <v>500</v>
       </c>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B21, $C$2:$C$718, C21, $D$2:$D$718, D21, $E$2:$E$718, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22931,7 +22951,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B22, $C$2:$C$718, C22, $D$2:$D$718, D22, $E$2:$E$718, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22"/>
@@ -22979,7 +22999,7 @@
         <v>300</v>
       </c>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B23, $C$2:$C$718, C23, $D$2:$D$718, D23, $E$2:$E$718, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23018,7 +23038,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B24, $C$2:$C$718, C24, $D$2:$D$718, D24, $E$2:$E$718, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -23059,7 +23079,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B25, $C$2:$C$718, C25, $D$2:$D$718, D25, $E$2:$E$718, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25"/>
@@ -23107,7 +23127,7 @@
         <v>516</v>
       </c>
       <c r="N26" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B26, $C$2:$C$718, C26, $D$2:$D$718, D26, $E$2:$E$718, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23153,7 +23173,7 @@
         <v>300</v>
       </c>
       <c r="N27" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B27, $C$2:$C$718, C27, $D$2:$D$718, D27, $E$2:$E$718, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P27" s="25"/>
@@ -23201,7 +23221,7 @@
         <v>175</v>
       </c>
       <c r="N28" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B28, $C$2:$C$718, C28, $D$2:$D$718, D28, $E$2:$E$718, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23240,7 +23260,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B29, $C$2:$C$718, C29, $D$2:$D$718, D29, $E$2:$E$718, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23279,7 +23299,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B30, $C$2:$C$718, C30, $D$2:$D$718, D30, $E$2:$E$718, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30"/>
@@ -23320,7 +23340,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B31, $C$2:$C$718, C31, $D$2:$D$718, D31, $E$2:$E$718, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -23361,7 +23381,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B32, $C$2:$C$718, C32, $D$2:$D$718, D32, $E$2:$E$718, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
@@ -23400,7 +23420,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B33, $C$2:$C$718, C33, $D$2:$D$718, D33, $E$2:$E$718, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -23438,7 +23458,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B34, $C$2:$C$718, C34, $D$2:$D$718, D34, $E$2:$E$718, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -23479,7 +23499,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B35, $C$2:$C$718, C35, $D$2:$D$718, D35, $E$2:$E$718, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35"/>
@@ -23528,7 +23548,7 @@
         <v>225</v>
       </c>
       <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B36, $C$2:$C$718, C36, $D$2:$D$718, D36, $E$2:$E$718, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23574,7 +23594,7 @@
         <v>525</v>
       </c>
       <c r="N37" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B37, $C$2:$C$718, C37, $D$2:$D$718, D37, $E$2:$E$718, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23620,7 +23640,7 @@
         <v>650</v>
       </c>
       <c r="N38" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B38, $C$2:$C$718, C38, $D$2:$D$718, D38, $E$2:$E$718, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23657,7 +23677,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B39, $C$2:$C$718, C39, $D$2:$D$718, D39, $E$2:$E$718, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39"/>
@@ -23698,7 +23718,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B40, $C$2:$C$718, C40, $D$2:$D$718, D40, $E$2:$E$718, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40"/>
@@ -23737,7 +23757,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B41, $C$2:$C$718, C41, $D$2:$D$718, D41, $E$2:$E$718, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -23778,7 +23798,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B42, $C$2:$C$718, C42, $D$2:$D$718, D42, $E$2:$E$718, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P42"/>
@@ -23816,7 +23836,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B43, $C$2:$C$718, C43, $D$2:$D$718, D43, $E$2:$E$718, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43"/>
@@ -23864,7 +23884,7 @@
         <v>314</v>
       </c>
       <c r="N44" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B44, $C$2:$C$718, C44, $D$2:$D$718, D44, $E$2:$E$718, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23910,7 +23930,7 @@
         <v>300</v>
       </c>
       <c r="N45" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B45, $C$2:$C$718, C45, $D$2:$D$718, D45, $E$2:$E$718, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -23951,7 +23971,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B46, $C$2:$C$718, C46, $D$2:$D$718, D46, $E$2:$E$718, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -23992,7 +24012,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B47, $C$2:$C$718, C47, $D$2:$D$718, D47, $E$2:$E$718, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -24030,7 +24050,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B48, $C$2:$C$718, C48, $D$2:$D$718, D48, $E$2:$E$718, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48"/>
@@ -24071,7 +24091,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B49, $C$2:$C$718, C49, $D$2:$D$718, D49, $E$2:$E$718, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49"/>
@@ -24110,7 +24130,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B50, $C$2:$C$718, C50, $D$2:$D$718, D50, $E$2:$E$718, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50"/>
@@ -24149,7 +24169,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B51, $C$2:$C$718, C51, $D$2:$D$718, D51, $E$2:$E$718, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51"/>
@@ -24188,7 +24208,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B52, $C$2:$C$718, C52, $D$2:$D$718, D52, $E$2:$E$718, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52"/>
@@ -24229,7 +24249,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B53, $C$2:$C$718, C53, $D$2:$D$718, D53, $E$2:$E$718, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53"/>
@@ -24268,7 +24288,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B54, $C$2:$C$718, C54, $D$2:$D$718, D54, $E$2:$E$718, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -24307,7 +24327,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B55, $C$2:$C$718, C55, $D$2:$D$718, D55, $E$2:$E$718, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -24356,7 +24376,7 @@
         <v>540</v>
       </c>
       <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B56, $C$2:$C$718, C56, $D$2:$D$718, D56, $E$2:$E$718, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -24399,7 +24419,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B57, $C$2:$C$718, C57, $D$2:$D$718, D57, $E$2:$E$718, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -24438,7 +24458,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B58, $C$2:$C$718, C58, $D$2:$D$718, D58, $E$2:$E$718, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -24480,7 +24500,7 @@
         <v>3156</v>
       </c>
       <c r="N59" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B59, $C$2:$C$718, C59, $D$2:$D$718, D59, $E$2:$E$718, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P59" s="19"/>
@@ -24518,7 +24538,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B60, $C$2:$C$718, C60, $D$2:$D$718, D60, $E$2:$E$718, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24555,7 +24575,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B61, $C$2:$C$718, C61, $D$2:$D$718, D61, $E$2:$E$718, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24594,7 +24614,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B62, $C$2:$C$718, C62, $D$2:$D$718, D62, $E$2:$E$718, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24633,7 +24653,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B63, $C$2:$C$718, C63, $D$2:$D$718, D63, $E$2:$E$718, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24670,7 +24690,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B64, $C$2:$C$718, C64, $D$2:$D$718, D64, $E$2:$E$718, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24716,7 +24736,7 @@
         <v>10680</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B65, $C$2:$C$718, C65, $D$2:$D$718, D65, $E$2:$E$718, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65" s="10"/>
@@ -24755,7 +24775,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B66, $C$2:$C$718, C66, $D$2:$D$718, D66, $E$2:$E$718, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$718, B66, $C$2:$C$718, C66, $D$2:$D$718, D66, $E$2:$E$718, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -24794,7 +24814,7 @@
       <c r="L67" s="17"/>
       <c r="M67" s="17"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B67, $C$2:$C$718, C67, $D$2:$D$718, D67, $E$2:$E$718, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67"/>
@@ -24842,7 +24862,7 @@
         <v>10880</v>
       </c>
       <c r="N68" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B68, $C$2:$C$718, C68, $D$2:$D$718, D68, $E$2:$E$718, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24881,7 +24901,7 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B69, $C$2:$C$718, C69, $D$2:$D$718, D69, $E$2:$E$718, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
@@ -24922,7 +24942,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B70, $C$2:$C$718, C70, $D$2:$D$718, D70, $E$2:$E$718, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
@@ -24971,7 +24991,7 @@
         <v>100</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B71, $C$2:$C$718, C71, $D$2:$D$718, D71, $E$2:$E$718, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25005,7 +25025,7 @@
       </c>
       <c r="J72" s="36"/>
       <c r="N72" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B72, $C$2:$C$718, C72, $D$2:$D$718, D72, $E$2:$E$718, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25052,7 +25072,7 @@
         <v>200</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B73, $C$2:$C$718, C73, $D$2:$D$718, D73, $E$2:$E$718, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25098,7 +25118,7 @@
         <v>300</v>
       </c>
       <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B74, $C$2:$C$718, C74, $D$2:$D$718, D74, $E$2:$E$718, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25144,7 +25164,7 @@
         <v>646</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B75, $C$2:$C$718, C75, $D$2:$D$718, D75, $E$2:$E$718, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25183,7 +25203,7 @@
       <c r="L76" s="17"/>
       <c r="M76" s="17"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B76, $C$2:$C$718, C76, $D$2:$D$718, D76, $E$2:$E$718, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76"/>
@@ -25227,11 +25247,11 @@
         <v>39300</v>
       </c>
       <c r="M77" s="18">
-        <f t="shared" ref="M77:M83" si="0">ABS((D77*E77)-L77)</f>
+        <f t="shared" ref="M77:M83" si="2">ABS((D77*E77)-L77)</f>
         <v>18850</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B77, $C$2:$C$718, C77, $D$2:$D$718, D77, $E$2:$E$718, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25273,11 +25293,11 @@
         <v>11320</v>
       </c>
       <c r="M78" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>400</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B78, $C$2:$C$718, C78, $D$2:$D$718, D78, $E$2:$E$718, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="10"/>
@@ -25321,11 +25341,11 @@
         <v>8220</v>
       </c>
       <c r="M79" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B79, $C$2:$C$718, C79, $D$2:$D$718, D79, $E$2:$E$718, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79" s="41" t="s">
@@ -25370,11 +25390,11 @@
         <v>32200</v>
       </c>
       <c r="M80" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1200</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B80, $C$2:$C$718, C80, $D$2:$D$718, D80, $E$2:$E$718, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="10"/>
@@ -25419,11 +25439,11 @@
         <v>8970</v>
       </c>
       <c r="M81" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B81, $C$2:$C$718, C81, $D$2:$D$718, D81, $E$2:$E$718, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="10"/>
@@ -25467,11 +25487,11 @@
         <v>19730.5</v>
       </c>
       <c r="M82" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>504.5</v>
       </c>
       <c r="N82" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B82, $C$2:$C$718, C82, $D$2:$D$718, D82, $E$2:$E$718, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O82" s="41" t="s">
@@ -25517,11 +25537,11 @@
         <v>19690</v>
       </c>
       <c r="M83" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>545</v>
       </c>
       <c r="N83" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B83, $C$2:$C$718, C83, $D$2:$D$718, D83, $E$2:$E$718, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O83" s="41" t="s">
@@ -25564,7 +25584,7 @@
       <c r="L84" s="18"/>
       <c r="M84" s="18"/>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B84, $C$2:$C$718, C84, $D$2:$D$718, D84, $E$2:$E$718, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O84" s="10"/>
@@ -25612,7 +25632,7 @@
         <v>300</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B85, $C$2:$C$718, C85, $D$2:$D$718, D85, $E$2:$E$718, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25658,7 +25678,7 @@
         <v>250</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B86, $C$2:$C$718, C86, $D$2:$D$718, D86, $E$2:$E$718, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25704,7 +25724,7 @@
         <v>650</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B87, $C$2:$C$718, C87, $D$2:$D$718, D87, $E$2:$E$718, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87" s="41" t="s">
@@ -25746,7 +25766,7 @@
       <c r="L88" s="17"/>
       <c r="M88" s="17"/>
       <c r="N88" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B88, $C$2:$C$718, C88, $D$2:$D$718, D88, $E$2:$E$718, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O88"/>
@@ -25790,11 +25810,11 @@
         <v>5585</v>
       </c>
       <c r="M89" s="29">
-        <f t="shared" ref="M89:M110" si="1">ABS((D89*E89)-L89)</f>
+        <f t="shared" ref="M89:M110" si="3">ABS((D89*E89)-L89)</f>
         <v>395</v>
       </c>
       <c r="N89" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B89, $C$2:$C$718, C89, $D$2:$D$718, D89, $E$2:$E$718, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O89" s="41" t="s">
@@ -25840,11 +25860,11 @@
         <v>5730</v>
       </c>
       <c r="M90" s="29">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="N90" s="31" t="str">
         <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="N90" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B90, $C$2:$C$718, C90, $D$2:$D$718, D90, $E$2:$E$718, E90) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O90" s="41" t="s">
@@ -25890,11 +25910,11 @@
         <v>9170</v>
       </c>
       <c r="M91" s="29">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="N91" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B91, $C$2:$C$718, C91, $D$2:$D$718, D91, $E$2:$E$718, E91) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O91" s="41" t="s">
@@ -25939,11 +25959,11 @@
         <v>10249</v>
       </c>
       <c r="M92" s="18">
+        <f t="shared" si="3"/>
+        <v>4451</v>
+      </c>
+      <c r="N92" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>4451</v>
-      </c>
-      <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B92, $C$2:$C$718, C92, $D$2:$D$718, D92, $E$2:$E$718, E92) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O92" s="41" t="s">
@@ -25988,11 +26008,11 @@
         <v>4120</v>
       </c>
       <c r="M93" s="29">
+        <f t="shared" si="3"/>
+        <v>270</v>
+      </c>
+      <c r="N93" s="31" t="str">
         <f t="shared" si="1"/>
-        <v>270</v>
-      </c>
-      <c r="N93" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B93, $C$2:$C$718, C93, $D$2:$D$718, D93, $E$2:$E$718, E93) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O93" s="30" t="s">
@@ -26038,11 +26058,11 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M94" s="29">
+        <f t="shared" si="3"/>
+        <v>188.60000000000014</v>
+      </c>
+      <c r="N94" s="31" t="str">
         <f t="shared" si="1"/>
-        <v>188.60000000000014</v>
-      </c>
-      <c r="N94" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B94, $C$2:$C$718, C94, $D$2:$D$718, D94, $E$2:$E$718, E94) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O94" s="30" t="s">
@@ -26088,11 +26108,11 @@
         <v>14440</v>
       </c>
       <c r="M95" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N95" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B95, $C$2:$C$718, C95, $D$2:$D$718, D95, $E$2:$E$718, E95) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O95"/>
@@ -26135,11 +26155,11 @@
         <v>20010</v>
       </c>
       <c r="M96" s="18">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+      <c r="N96" t="str">
         <f t="shared" si="1"/>
-        <v>450</v>
-      </c>
-      <c r="N96" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B96, $C$2:$C$718, C96, $D$2:$D$718, D96, $E$2:$E$718, E96) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O96" s="10"/>
@@ -26183,11 +26203,11 @@
         <v>32900</v>
       </c>
       <c r="M97" s="18">
+        <f t="shared" si="3"/>
+        <v>1000</v>
+      </c>
+      <c r="N97" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-      <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B97, $C$2:$C$718, C97, $D$2:$D$718, D97, $E$2:$E$718, E97) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O97" s="10"/>
@@ -26231,11 +26251,11 @@
         <v>8420</v>
       </c>
       <c r="M98" s="47">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N98" s="25" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N98" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B98, $C$2:$C$718, C98, $D$2:$D$718, D98, $E$2:$E$718, E98) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O98" s="25"/>
@@ -26281,11 +26301,11 @@
         <v>11660</v>
       </c>
       <c r="M99" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N99" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B99, $C$2:$C$718, C99, $D$2:$D$718, D99, $E$2:$E$718, E99) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O99" s="41" t="s">
@@ -26330,11 +26350,11 @@
         <v>39300</v>
       </c>
       <c r="M100" s="18">
+        <f t="shared" si="3"/>
+        <v>18350</v>
+      </c>
+      <c r="N100" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>18350</v>
-      </c>
-      <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B100, $C$2:$C$718, C100, $D$2:$D$718, D100, $E$2:$E$718, E100) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26376,11 +26396,11 @@
         <v>5755</v>
       </c>
       <c r="M101" s="29">
+        <f t="shared" si="3"/>
+        <v>275</v>
+      </c>
+      <c r="N101" s="31" t="str">
         <f t="shared" si="1"/>
-        <v>275</v>
-      </c>
-      <c r="N101" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B101, $C$2:$C$718, C101, $D$2:$D$718, D101, $E$2:$E$718, E101) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -26422,11 +26442,11 @@
         <v>5805</v>
       </c>
       <c r="M102" s="29">
+        <f t="shared" si="3"/>
+        <v>225</v>
+      </c>
+      <c r="N102" s="31" t="str">
         <f t="shared" si="1"/>
-        <v>225</v>
-      </c>
-      <c r="N102" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B102, $C$2:$C$718, C102, $D$2:$D$718, D102, $E$2:$E$718, E102) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -26468,11 +26488,11 @@
         <v>15075</v>
       </c>
       <c r="M103" s="18">
+        <f t="shared" si="3"/>
+        <v>645</v>
+      </c>
+      <c r="N103" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>645</v>
-      </c>
-      <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B103, $C$2:$C$718, C103, $D$2:$D$718, D103, $E$2:$E$718, E103) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O103" s="41" t="s">
@@ -26517,11 +26537,11 @@
         <v>20260</v>
       </c>
       <c r="M104" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N104" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N104" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B104, $C$2:$C$718, C104, $D$2:$D$718, D104, $E$2:$E$718, E104) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O104"/>
@@ -26565,11 +26585,11 @@
         <v>8700</v>
       </c>
       <c r="M105" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N105" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B105, $C$2:$C$718, C105, $D$2:$D$718, D105, $E$2:$E$718, E105) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26611,11 +26631,11 @@
         <v>14100</v>
       </c>
       <c r="M106" s="18">
+        <f t="shared" si="3"/>
+        <v>500</v>
+      </c>
+      <c r="N106" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B106, $C$2:$C$718, C106, $D$2:$D$718, D106, $E$2:$E$718, E106) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26657,11 +26677,11 @@
         <v>6367.2</v>
       </c>
       <c r="M107" s="18">
+        <f t="shared" si="3"/>
+        <v>300.80000000000018</v>
+      </c>
+      <c r="N107" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300.80000000000018</v>
-      </c>
-      <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B107, $C$2:$C$718, C107, $D$2:$D$718, D107, $E$2:$E$718, E107) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26703,11 +26723,11 @@
         <v>16755</v>
       </c>
       <c r="M108" s="18">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+      <c r="N108" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>295</v>
-      </c>
-      <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B108, $C$2:$C$718, C108, $D$2:$D$718, D108, $E$2:$E$718, E108) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26749,11 +26769,11 @@
         <v>4852</v>
       </c>
       <c r="M109" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N109" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B109, $C$2:$C$718, C109, $D$2:$D$718, D109, $E$2:$E$718, E109) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O109" s="10"/>
@@ -26797,11 +26817,11 @@
         <v>9170</v>
       </c>
       <c r="M110" s="29">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N110" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B110, $C$2:$C$718, C110, $D$2:$D$718, D110, $E$2:$E$718, E110) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26835,7 +26855,7 @@
       </c>
       <c r="J111" s="36"/>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B111, $C$2:$C$718, C111, $D$2:$D$718, D111, $E$2:$E$718, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26881,7 +26901,7 @@
         <v>650</v>
       </c>
       <c r="N112" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B112, $C$2:$C$718, C112, $D$2:$D$718, D112, $E$2:$E$718, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26917,7 +26937,7 @@
         <v>118</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B113, $C$2:$C$718, C113, $D$2:$D$718, D113, $E$2:$E$718, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26963,7 +26983,7 @@
         <v>710.99999999999636</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B114, $C$2:$C$718, C114, $D$2:$D$718, D114, $E$2:$E$718, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O114" s="10"/>
@@ -27011,7 +27031,7 @@
         <v>500</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B115, $C$2:$C$718, C115, $D$2:$D$718, D115, $E$2:$E$718, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27057,7 +27077,7 @@
         <v>1400</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B116, $C$2:$C$718, C116, $D$2:$D$718, D116, $E$2:$E$718, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="41" t="s">
@@ -27106,7 +27126,7 @@
         <v>280</v>
       </c>
       <c r="N117" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B117, $C$2:$C$718, C117, $D$2:$D$718, D117, $E$2:$E$718, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="41" t="s">
@@ -27143,7 +27163,7 @@
       </c>
       <c r="J118" s="36"/>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B118, $C$2:$C$718, C118, $D$2:$D$718, D118, $E$2:$E$718, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="41" t="s">
@@ -27193,7 +27213,7 @@
         <v>300</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B119, $C$2:$C$718, C119, $D$2:$D$718, D119, $E$2:$E$718, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P119" s="31"/>
@@ -27240,7 +27260,7 @@
         <v>1200</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B120, $C$2:$C$718, C120, $D$2:$D$718, D120, $E$2:$E$718, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27276,7 +27296,7 @@
         <v>117</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B121, $C$2:$C$718, C121, $D$2:$D$718, D121, $E$2:$E$718, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27318,11 +27338,11 @@
         <v>5370</v>
       </c>
       <c r="M122" s="29">
-        <f t="shared" ref="M122:M127" si="2">ABS((D122*E122)-L122)</f>
+        <f t="shared" ref="M122:M127" si="4">ABS((D122*E122)-L122)</f>
         <v>320</v>
       </c>
       <c r="N122" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B122, $C$2:$C$718, C122, $D$2:$D$718, D122, $E$2:$E$718, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="31"/>
@@ -27366,11 +27386,11 @@
         <v>2610</v>
       </c>
       <c r="M123" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>235</v>
       </c>
       <c r="N123" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B123, $C$2:$C$718, C123, $D$2:$D$718, D123, $E$2:$E$718, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O123" s="31"/>
@@ -27414,11 +27434,11 @@
         <v>9270</v>
       </c>
       <c r="M124" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B124, $C$2:$C$718, C124, $D$2:$D$718, D124, $E$2:$E$718, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P124" s="19"/>
@@ -27461,11 +27481,11 @@
         <v>3400</v>
       </c>
       <c r="M125" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B125, $C$2:$C$718, C125, $D$2:$D$718, D125, $E$2:$E$718, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27507,11 +27527,11 @@
         <v>8820</v>
       </c>
       <c r="M126" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N126" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B126, $C$2:$C$718, C126, $D$2:$D$718, D126, $E$2:$E$718, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27553,11 +27573,11 @@
         <v>36946</v>
       </c>
       <c r="M127" s="29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>934</v>
       </c>
       <c r="N127" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B127, $C$2:$C$718, C127, $D$2:$D$718, D127, $E$2:$E$718, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27594,7 +27614,7 @@
       <c r="L128" s="18"/>
       <c r="M128" s="18"/>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B128, $C$2:$C$718, C128, $D$2:$D$718, D128, $E$2:$E$718, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="25"/>
@@ -27638,11 +27658,11 @@
         <v>4080</v>
       </c>
       <c r="M129" s="18">
-        <f t="shared" ref="M129:M144" si="3">ABS((D129*E129)-L129)</f>
+        <f t="shared" ref="M129:M144" si="5">ABS((D129*E129)-L129)</f>
         <v>300</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B129, $C$2:$C$718, C129, $D$2:$D$718, D129, $E$2:$E$718, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27684,11 +27704,11 @@
         <v>73800</v>
       </c>
       <c r="M130" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>48320</v>
       </c>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B130, $C$2:$C$718, C130, $D$2:$D$718, D130, $E$2:$E$718, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="6">IF(COUNTIFS( $B$2:$B$718, B130, $C$2:$C$718, C130, $D$2:$D$718, D130, $E$2:$E$718, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="41" t="s">
@@ -27733,11 +27753,11 @@
         <v>10410</v>
       </c>
       <c r="M131" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B131, $C$2:$C$718, C131, $D$2:$D$718, D131, $E$2:$E$718, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="31"/>
@@ -27780,11 +27800,11 @@
         <v>7578</v>
       </c>
       <c r="M132" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>294</v>
       </c>
       <c r="N132" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B132, $C$2:$C$718, C132, $D$2:$D$718, D132, $E$2:$E$718, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -27826,11 +27846,11 @@
         <v>7578</v>
       </c>
       <c r="M133" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>294</v>
       </c>
       <c r="N133" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B133, $C$2:$C$718, C133, $D$2:$D$718, D133, $E$2:$E$718, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -27872,11 +27892,11 @@
         <v>4968</v>
       </c>
       <c r="M134" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>280</v>
       </c>
       <c r="N134" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B134, $C$2:$C$718, C134, $D$2:$D$718, D134, $E$2:$E$718, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="31"/>
@@ -27920,11 +27940,11 @@
         <v>2899.25</v>
       </c>
       <c r="M135" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300.75</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B135, $C$2:$C$718, C135, $D$2:$D$718, D135, $E$2:$E$718, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27966,11 +27986,11 @@
         <v>14400</v>
       </c>
       <c r="M136" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B136, $C$2:$C$718, C136, $D$2:$D$718, D136, $E$2:$E$718, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28012,11 +28032,11 @@
         <v>33950</v>
       </c>
       <c r="M137" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>850</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B137, $C$2:$C$718, C137, $D$2:$D$718, D137, $E$2:$E$718, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28058,11 +28078,11 @@
         <v>5905</v>
       </c>
       <c r="M138" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>275</v>
       </c>
       <c r="N138" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B138, $C$2:$C$718, C138, $D$2:$D$718, D138, $E$2:$E$718, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28104,11 +28124,11 @@
         <v>16580</v>
       </c>
       <c r="M139" s="47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>750</v>
       </c>
       <c r="N139" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B139, $C$2:$C$718, C139, $D$2:$D$718, D139, $E$2:$E$718, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="25"/>
@@ -28154,11 +28174,11 @@
         <v>10814</v>
       </c>
       <c r="M140" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>501</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B140, $C$2:$C$718, C140, $D$2:$D$718, D140, $E$2:$E$718, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="41" t="s">
@@ -28204,11 +28224,11 @@
         <v>17150</v>
       </c>
       <c r="M141" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B141, $C$2:$C$718, C141, $D$2:$D$718, D141, $E$2:$E$718, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28250,11 +28270,11 @@
         <v>4680</v>
       </c>
       <c r="M142" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>140</v>
       </c>
       <c r="N142" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B142, $C$2:$C$718, C142, $D$2:$D$718, D142, $E$2:$E$718, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="P142" s="31"/>
@@ -28297,11 +28317,11 @@
         <v>4520</v>
       </c>
       <c r="M143" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N143" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B143, $C$2:$C$718, C143, $D$2:$D$718, D143, $E$2:$E$718, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -28343,11 +28363,11 @@
         <v>10510</v>
       </c>
       <c r="M144" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B144, $C$2:$C$718, C144, $D$2:$D$718, D144, $E$2:$E$718, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28386,7 +28406,7 @@
       <c r="L145" s="18"/>
       <c r="M145" s="18"/>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B145, $C$2:$C$718, C145, $D$2:$D$718, D145, $E$2:$E$718, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O145" s="10"/>
@@ -28430,11 +28450,11 @@
         <v>37480</v>
       </c>
       <c r="M146" s="18">
-        <f t="shared" ref="M146:M156" si="4">ABS((D146*E146)-L146)</f>
+        <f t="shared" ref="M146:M156" si="7">ABS((D146*E146)-L146)</f>
         <v>1000</v>
       </c>
       <c r="N146" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B146, $C$2:$C$718, C146, $D$2:$D$718, D146, $E$2:$E$718, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P146" s="31"/>
@@ -28477,11 +28497,11 @@
         <v>2105</v>
       </c>
       <c r="M147" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>250</v>
       </c>
       <c r="N147" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B147, $C$2:$C$718, C147, $D$2:$D$718, D147, $E$2:$E$718, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28523,11 +28543,11 @@
         <v>12510</v>
       </c>
       <c r="M148" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>290</v>
       </c>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B148, $C$2:$C$718, C148, $D$2:$D$718, D148, $E$2:$E$718, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28569,11 +28589,11 @@
         <v>9470</v>
       </c>
       <c r="M149" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B149, $C$2:$C$718, C149, $D$2:$D$718, D149, $E$2:$E$718, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28615,11 +28635,11 @@
         <v>20070</v>
       </c>
       <c r="M150" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>810</v>
       </c>
       <c r="N150" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B150, $C$2:$C$718, C150, $D$2:$D$718, D150, $E$2:$E$718, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28661,11 +28681,11 @@
         <v>14650</v>
       </c>
       <c r="M151" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>450</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B151, $C$2:$C$718, C151, $D$2:$D$718, D151, $E$2:$E$718, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28707,11 +28727,11 @@
         <v>3810</v>
       </c>
       <c r="M152" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N152" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B152, $C$2:$C$718, C152, $D$2:$D$718, D152, $E$2:$E$718, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28753,11 +28773,11 @@
         <v>3005</v>
       </c>
       <c r="M153" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>240</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B153, $C$2:$C$718, C153, $D$2:$D$718, D153, $E$2:$E$718, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="10"/>
@@ -28801,11 +28821,11 @@
         <v>6105</v>
       </c>
       <c r="M154" s="29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>150</v>
       </c>
       <c r="N154" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B154, $C$2:$C$718, C154, $D$2:$D$718, D154, $E$2:$E$718, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -28847,11 +28867,11 @@
         <v>6005</v>
       </c>
       <c r="M155" s="29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>250</v>
       </c>
       <c r="N155" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B155, $C$2:$C$718, C155, $D$2:$D$718, D155, $E$2:$E$718, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -28893,11 +28913,11 @@
         <v>73800</v>
       </c>
       <c r="M156" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>47900</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B156, $C$2:$C$718, C156, $D$2:$D$718, D156, $E$2:$E$718, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O156" s="41" t="s">
@@ -28934,7 +28954,7 @@
       </c>
       <c r="J157" s="36"/>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B157, $C$2:$C$718, C157, $D$2:$D$718, D157, $E$2:$E$718, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28975,7 +28995,7 @@
       <c r="L158" s="18"/>
       <c r="M158" s="18"/>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B158, $C$2:$C$718, C158, $D$2:$D$718, D158, $E$2:$E$718, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O158" s="10"/>
@@ -29019,11 +29039,11 @@
         <v>25300</v>
       </c>
       <c r="M159" s="18">
-        <f t="shared" ref="M159:M165" si="5">ABS((D159*E159)-L159)</f>
+        <f t="shared" ref="M159:M165" si="8">ABS((D159*E159)-L159)</f>
         <v>650</v>
       </c>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B159, $C$2:$C$718, C159, $D$2:$D$718, D159, $E$2:$E$718, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="41" t="s">
@@ -29069,11 +29089,11 @@
         <v>12480</v>
       </c>
       <c r="M160" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>495</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B160, $C$2:$C$718, C160, $D$2:$D$718, D160, $E$2:$E$718, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="41" t="s">
@@ -29118,11 +29138,11 @@
         <v>11175</v>
       </c>
       <c r="M161" s="29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N161" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B161, $C$2:$C$718, C161, $D$2:$D$718, D161, $E$2:$E$718, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="31"/>
@@ -29166,11 +29186,11 @@
         <v>4402</v>
       </c>
       <c r="M162" s="29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>188</v>
       </c>
       <c r="N162" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B162, $C$2:$C$718, C162, $D$2:$D$718, D162, $E$2:$E$718, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O162" s="31"/>
@@ -29214,11 +29234,11 @@
         <v>7200</v>
       </c>
       <c r="M163" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>250</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B163, $C$2:$C$718, C163, $D$2:$D$718, D163, $E$2:$E$718, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29260,11 +29280,11 @@
         <v>4170</v>
       </c>
       <c r="M164" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N164" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B164, $C$2:$C$718, C164, $D$2:$D$718, D164, $E$2:$E$718, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29306,11 +29326,11 @@
         <v>17040</v>
       </c>
       <c r="M165" s="18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>880</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B165, $C$2:$C$718, C165, $D$2:$D$718, D165, $E$2:$E$718, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O165" s="41" t="s">
@@ -29347,7 +29367,7 @@
       </c>
       <c r="J166" s="36"/>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B166, $C$2:$C$718, C166, $D$2:$D$718, D166, $E$2:$E$718, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29383,7 +29403,7 @@
         <v>195</v>
       </c>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B167, $C$2:$C$718, C167, $D$2:$D$718, D167, $E$2:$E$718, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29429,7 +29449,7 @@
         <v>300</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B168, $C$2:$C$718, C168, $D$2:$D$718, D168, $E$2:$E$718, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29475,7 +29495,7 @@
         <v>500</v>
       </c>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B169, $C$2:$C$718, C169, $D$2:$D$718, D169, $E$2:$E$718, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O169" s="42" t="s">
@@ -29516,7 +29536,7 @@
       <c r="L170" s="18"/>
       <c r="M170" s="18"/>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B170, $C$2:$C$718, C170, $D$2:$D$718, D170, $E$2:$E$718, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O170" s="10"/>
@@ -29564,7 +29584,7 @@
         <v>300</v>
       </c>
       <c r="N171" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B171, $C$2:$C$718, C171, $D$2:$D$718, D171, $E$2:$E$718, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O171" s="41" t="s">
@@ -29614,7 +29634,7 @@
         <v>940</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B172, $C$2:$C$718, C172, $D$2:$D$718, D172, $E$2:$E$718, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29650,7 +29670,7 @@
         <v>118</v>
       </c>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B173, $C$2:$C$718, C173, $D$2:$D$718, D173, $E$2:$E$718, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O173" s="41" t="s">
@@ -29700,7 +29720,7 @@
         <v>260</v>
       </c>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B174, $C$2:$C$718, C174, $D$2:$D$718, D174, $E$2:$E$718, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29746,7 +29766,7 @@
         <v>360</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B175, $C$2:$C$718, C175, $D$2:$D$718, D175, $E$2:$E$718, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29792,7 +29812,7 @@
         <v>650</v>
       </c>
       <c r="N176" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B176, $C$2:$C$718, C176, $D$2:$D$718, D176, $E$2:$E$718, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O176"/>
@@ -29828,7 +29848,7 @@
       </c>
       <c r="J177" s="36"/>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B177, $C$2:$C$718, C177, $D$2:$D$718, D177, $E$2:$E$718, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="31"/>
@@ -29865,7 +29885,7 @@
         <v>117</v>
       </c>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B178, $C$2:$C$718, C178, $D$2:$D$718, D178, $E$2:$E$718, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29911,7 +29931,7 @@
         <v>816</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B179, $C$2:$C$718, C179, $D$2:$D$718, D179, $E$2:$E$718, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29957,7 +29977,7 @@
         <v>1700</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B180, $C$2:$C$718, C180, $D$2:$D$718, D180, $E$2:$E$718, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="31"/>
@@ -30004,7 +30024,7 @@
         <v>47480</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B181, $C$2:$C$718, C181, $D$2:$D$718, D181, $E$2:$E$718, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O181" s="10"/>
@@ -30052,7 +30072,7 @@
         <v>300</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B182, $C$2:$C$718, C182, $D$2:$D$718, D182, $E$2:$E$718, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P182" s="26"/>
@@ -30089,7 +30109,7 @@
         <v>118</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B183, $C$2:$C$718, C183, $D$2:$D$718, D183, $E$2:$E$718, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30135,7 +30155,7 @@
         <v>340</v>
       </c>
       <c r="N184" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B184, $C$2:$C$718, C184, $D$2:$D$718, D184, $E$2:$E$718, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30174,7 +30194,7 @@
       <c r="L185" s="47"/>
       <c r="M185" s="47"/>
       <c r="N185" s="25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B185, $C$2:$C$718, C185, $D$2:$D$718, D185, $E$2:$E$718, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="25"/>
@@ -30217,7 +30237,7 @@
       <c r="L186" s="18"/>
       <c r="M186" s="18"/>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B186, $C$2:$C$718, C186, $D$2:$D$718, D186, $E$2:$E$718, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O186" s="10"/>
@@ -30255,7 +30275,7 @@
         <v>117</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B187, $C$2:$C$718, C187, $D$2:$D$718, D187, $E$2:$E$718, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30301,7 +30321,7 @@
         <v>300</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B188, $C$2:$C$718, C188, $D$2:$D$718, D188, $E$2:$E$718, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O188" s="41" t="s">
@@ -30341,7 +30361,7 @@
         <v>118</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B189, $C$2:$C$718, C189, $D$2:$D$718, D189, $E$2:$E$718, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O189" s="41" t="s">
@@ -30390,7 +30410,7 @@
         <v>800</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B190, $C$2:$C$718, C190, $D$2:$D$718, D190, $E$2:$E$718, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O190" s="41" t="s">
@@ -30439,7 +30459,7 @@
         <v>300</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B191, $C$2:$C$718, C191, $D$2:$D$718, D191, $E$2:$E$718, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30485,7 +30505,7 @@
         <v>646</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B192, $C$2:$C$718, C192, $D$2:$D$718, D192, $E$2:$E$718, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="41" t="s">
@@ -30522,7 +30542,7 @@
       </c>
       <c r="J193" s="36"/>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B193, $C$2:$C$718, C193, $D$2:$D$718, D193, $E$2:$E$718, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30568,7 +30588,7 @@
         <v>651</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B194, $C$2:$C$718, C194, $D$2:$D$718, D194, $E$2:$E$718, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="9">IF(COUNTIFS( $B$2:$B$718, B194, $C$2:$C$718, C194, $D$2:$D$718, D194, $E$2:$E$718, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -30614,7 +30634,7 @@
         <v>450</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B195, $C$2:$C$718, C195, $D$2:$D$718, D195, $E$2:$E$718, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30650,7 +30670,7 @@
         <v>117</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B196, $C$2:$C$718, C196, $D$2:$D$718, D196, $E$2:$E$718, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30696,7 +30716,7 @@
         <v>300</v>
       </c>
       <c r="N197" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B197, $C$2:$C$718, C197, $D$2:$D$718, D197, $E$2:$E$718, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O197" s="41" t="s">
@@ -30745,7 +30765,7 @@
         <v>253</v>
       </c>
       <c r="N198" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B198, $C$2:$C$718, C198, $D$2:$D$718, D198, $E$2:$E$718, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
       <c r="O198" s="41" t="s">
@@ -30794,7 +30814,7 @@
         <v>355.5</v>
       </c>
       <c r="N199" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B199, $C$2:$C$718, C199, $D$2:$D$718, D199, $E$2:$E$718, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
       <c r="O199" s="41" t="s">
@@ -30834,7 +30854,7 @@
         <v>55</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B200, $C$2:$C$718, C200, $D$2:$D$718, D200, $E$2:$E$718, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30880,7 +30900,7 @@
         <v>300</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B201, $C$2:$C$718, C201, $D$2:$D$718, D201, $E$2:$E$718, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30926,7 +30946,7 @@
         <v>320</v>
       </c>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B202, $C$2:$C$718, C202, $D$2:$D$718, D202, $E$2:$E$718, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30972,7 +30992,7 @@
         <v>448</v>
       </c>
       <c r="N203" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B203, $C$2:$C$718, C203, $D$2:$D$718, D203, $E$2:$E$718, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31018,7 +31038,7 @@
         <v>650</v>
       </c>
       <c r="N204" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B204, $C$2:$C$718, C204, $D$2:$D$718, D204, $E$2:$E$718, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P204" s="31"/>
@@ -31065,7 +31085,7 @@
         <v>400</v>
       </c>
       <c r="N205" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B205, $C$2:$C$718, C205, $D$2:$D$718, D205, $E$2:$E$718, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O205" s="10"/>
@@ -31103,7 +31123,7 @@
         <v>118</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B206, $C$2:$C$718, C206, $D$2:$D$718, D206, $E$2:$E$718, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="31"/>
@@ -31138,7 +31158,7 @@
       </c>
       <c r="J207" s="36"/>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B207, $C$2:$C$718, C207, $D$2:$D$718, D207, $E$2:$E$718, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="31"/>
@@ -31185,7 +31205,7 @@
         <v>650</v>
       </c>
       <c r="N208" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B208, $C$2:$C$718, C208, $D$2:$D$718, D208, $E$2:$E$718, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P208" s="31"/>
@@ -31227,7 +31247,7 @@
       <c r="L209" s="17"/>
       <c r="M209" s="17"/>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B209, $C$2:$C$718, C209, $D$2:$D$718, D209, $E$2:$E$718, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31261,7 +31281,7 @@
       </c>
       <c r="J210" s="36"/>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B210, $C$2:$C$718, C210, $D$2:$D$718, D210, $E$2:$E$718, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31297,7 +31317,7 @@
         <v>118</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B211, $C$2:$C$718, C211, $D$2:$D$718, D211, $E$2:$E$718, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31331,7 +31351,7 @@
       </c>
       <c r="J212" s="36"/>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B212, $C$2:$C$718, C212, $D$2:$D$718, D212, $E$2:$E$718, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31367,7 +31387,7 @@
         <v>117</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B213, $C$2:$C$718, C213, $D$2:$D$718, D213, $E$2:$E$718, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31406,7 +31426,7 @@
       <c r="L214" s="18"/>
       <c r="M214" s="18"/>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B214, $C$2:$C$718, C214, $D$2:$D$718, D214, $E$2:$E$718, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="10"/>
@@ -31454,7 +31474,7 @@
         <v>527.5</v>
       </c>
       <c r="N215" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B215, $C$2:$C$718, C215, $D$2:$D$718, D215, $E$2:$E$718, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="31"/>
@@ -31497,7 +31517,7 @@
       <c r="L216" s="29"/>
       <c r="M216" s="29"/>
       <c r="N216" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B216, $C$2:$C$718, C216, $D$2:$D$718, D216, $E$2:$E$718, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O216" s="31"/>
@@ -31538,7 +31558,7 @@
         <v>146</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B217, $C$2:$C$718, C217, $D$2:$D$718, D217, $E$2:$E$718, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31584,7 +31604,7 @@
         <v>250</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B218, $C$2:$C$718, C218, $D$2:$D$718, D218, $E$2:$E$718, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P218" s="31"/>
@@ -31621,7 +31641,7 @@
         <v>154</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B219, $C$2:$C$718, C219, $D$2:$D$718, D219, $E$2:$E$718, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31667,7 +31687,7 @@
         <v>480</v>
       </c>
       <c r="N220" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B220, $C$2:$C$718, C220, $D$2:$D$718, D220, $E$2:$E$718, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31703,7 +31723,7 @@
         <v>118</v>
       </c>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B221, $C$2:$C$718, C221, $D$2:$D$718, D221, $E$2:$E$718, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="31"/>
@@ -31740,7 +31760,7 @@
         <v>117</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B222, $C$2:$C$718, C222, $D$2:$D$718, D222, $E$2:$E$718, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31786,7 +31806,7 @@
         <v>370</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B223, $C$2:$C$718, C223, $D$2:$D$718, D223, $E$2:$E$718, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P223" s="31"/>
@@ -31821,7 +31841,7 @@
       </c>
       <c r="J224" s="36"/>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B224, $C$2:$C$718, C224, $D$2:$D$718, D224, $E$2:$E$718, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31857,7 +31877,7 @@
         <v>118</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B225, $C$2:$C$718, C225, $D$2:$D$718, D225, $E$2:$E$718, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31891,7 +31911,7 @@
       </c>
       <c r="J226" s="36"/>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B226, $C$2:$C$718, C226, $D$2:$D$718, D226, $E$2:$E$718, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31927,7 +31947,7 @@
         <v>118</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B227, $C$2:$C$718, C227, $D$2:$D$718, D227, $E$2:$E$718, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31973,7 +31993,7 @@
         <v>800</v>
       </c>
       <c r="N228" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B228, $C$2:$C$718, C228, $D$2:$D$718, D228, $E$2:$E$718, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32007,7 +32027,7 @@
       </c>
       <c r="J229" s="36"/>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B229, $C$2:$C$718, C229, $D$2:$D$718, D229, $E$2:$E$718, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P229" s="31"/>
@@ -32047,7 +32067,7 @@
         <v>144</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B230, $C$2:$C$718, C230, $D$2:$D$718, D230, $E$2:$E$718, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32083,7 +32103,7 @@
         <v>117</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B231, $C$2:$C$718, C231, $D$2:$D$718, D231, $E$2:$E$718, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32129,7 +32149,7 @@
         <v>300</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B232, $C$2:$C$718, C232, $D$2:$D$718, D232, $E$2:$E$718, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32175,7 +32195,7 @@
         <v>500</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B233, $C$2:$C$718, C233, $D$2:$D$718, D233, $E$2:$E$718, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O233" s="41" t="s">
@@ -32212,7 +32232,7 @@
       </c>
       <c r="J234" s="36"/>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B234, $C$2:$C$718, C234, $D$2:$D$718, D234, $E$2:$E$718, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32246,7 +32266,7 @@
       </c>
       <c r="J235" s="36"/>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B235, $C$2:$C$718, C235, $D$2:$D$718, D235, $E$2:$E$718, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32282,7 +32302,7 @@
         <v>117</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B236, $C$2:$C$718, C236, $D$2:$D$718, D236, $E$2:$E$718, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32328,7 +32348,7 @@
         <v>268</v>
       </c>
       <c r="N237" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B237, $C$2:$C$718, C237, $D$2:$D$718, D237, $E$2:$E$718, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32362,7 +32382,7 @@
       </c>
       <c r="J238" s="36"/>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B238, $C$2:$C$718, C238, $D$2:$D$718, D238, $E$2:$E$718, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32398,7 +32418,7 @@
         <v>118</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B239, $C$2:$C$718, C239, $D$2:$D$718, D239, $E$2:$E$718, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O239" s="31"/>
@@ -32445,7 +32465,7 @@
         <v>650</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B240, $C$2:$C$718, C240, $D$2:$D$718, D240, $E$2:$E$718, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O240" s="31"/>
@@ -32482,7 +32502,7 @@
         <v>118</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B241, $C$2:$C$718, C241, $D$2:$D$718, D241, $E$2:$E$718, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32528,7 +32548,7 @@
         <v>300</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B242, $C$2:$C$718, C242, $D$2:$D$718, D242, $E$2:$E$718, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32574,7 +32594,7 @@
         <v>1800</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B243, $C$2:$C$718, C243, $D$2:$D$718, D243, $E$2:$E$718, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32610,7 +32630,7 @@
         <v>117</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B244, $C$2:$C$718, C244, $D$2:$D$718, D244, $E$2:$E$718, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P244" s="31"/>
@@ -32657,7 +32677,7 @@
         <v>250</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B245, $C$2:$C$718, C245, $D$2:$D$718, D245, $E$2:$E$718, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32691,7 +32711,7 @@
       </c>
       <c r="J246" s="36"/>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B246, $C$2:$C$718, C246, $D$2:$D$718, D246, $E$2:$E$718, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32727,7 +32747,7 @@
         <v>117</v>
       </c>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B247, $C$2:$C$718, C247, $D$2:$D$718, D247, $E$2:$E$718, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32773,7 +32793,7 @@
         <v>260</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B248, $C$2:$C$718, C248, $D$2:$D$718, D248, $E$2:$E$718, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32819,7 +32839,7 @@
         <v>300</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B249, $C$2:$C$718, C249, $D$2:$D$718, D249, $E$2:$E$718, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32853,7 +32873,7 @@
       </c>
       <c r="J250" s="36"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B250, $C$2:$C$718, C250, $D$2:$D$718, D250, $E$2:$E$718, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32899,7 +32919,7 @@
         <v>250</v>
       </c>
       <c r="N251" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B251, $C$2:$C$718, C251, $D$2:$D$718, D251, $E$2:$E$718, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32938,7 +32958,7 @@
       <c r="L252" s="18"/>
       <c r="M252" s="18"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B252, $C$2:$C$718, C252, $D$2:$D$718, D252, $E$2:$E$718, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O252" s="10"/>
@@ -32979,7 +32999,7 @@
       <c r="L253" s="18"/>
       <c r="M253" s="18"/>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B253, $C$2:$C$718, C253, $D$2:$D$718, D253, $E$2:$E$718, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O253" s="10"/>
@@ -33015,7 +33035,7 @@
       </c>
       <c r="J254" s="36"/>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B254, $C$2:$C$718, C254, $D$2:$D$718, D254, $E$2:$E$718, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33051,7 +33071,7 @@
         <v>118</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B255, $C$2:$C$718, C255, $D$2:$D$718, D255, $E$2:$E$718, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33097,7 +33117,7 @@
         <v>300</v>
       </c>
       <c r="N256" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B256, $C$2:$C$718, C256, $D$2:$D$718, D256, $E$2:$E$718, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33131,7 +33151,7 @@
       </c>
       <c r="J257" s="36"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B257, $C$2:$C$718, C257, $D$2:$D$718, D257, $E$2:$E$718, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33165,7 +33185,7 @@
       </c>
       <c r="J258" s="36"/>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B258, $C$2:$C$718, C258, $D$2:$D$718, D258, $E$2:$E$718, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N293" si="10">IF(COUNTIFS( $B$2:$B$718, B258, $C$2:$C$718, C258, $D$2:$D$718, D258, $E$2:$E$718, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P258" s="31"/>
@@ -33200,7 +33220,7 @@
       </c>
       <c r="J259" s="36"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B259, $C$2:$C$718, C259, $D$2:$D$718, D259, $E$2:$E$718, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33236,7 +33256,7 @@
         <v>117</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B260, $C$2:$C$718, C260, $D$2:$D$718, D260, $E$2:$E$718, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33270,7 +33290,7 @@
       </c>
       <c r="J261" s="36"/>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B261, $C$2:$C$718, C261, $D$2:$D$718, D261, $E$2:$E$718, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P261" s="31"/>
@@ -33317,7 +33337,7 @@
         <v>285</v>
       </c>
       <c r="N262" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B262, $C$2:$C$718, C262, $D$2:$D$718, D262, $E$2:$E$718, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33363,7 +33383,7 @@
         <v>726</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B263, $C$2:$C$718, C263, $D$2:$D$718, D263, $E$2:$E$718, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33399,7 +33419,7 @@
         <v>118</v>
       </c>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B264, $C$2:$C$718, C264, $D$2:$D$718, D264, $E$2:$E$718, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33436,7 +33456,7 @@
       <c r="L265" s="18"/>
       <c r="M265" s="18"/>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B265, $C$2:$C$718, C265, $D$2:$D$718, D265, $E$2:$E$718, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="10"/>
@@ -33474,7 +33494,7 @@
         <v>118</v>
       </c>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B266, $C$2:$C$718, C266, $D$2:$D$718, D266, $E$2:$E$718, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33508,7 +33528,7 @@
       </c>
       <c r="J267" s="36"/>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B267, $C$2:$C$718, C267, $D$2:$D$718, D267, $E$2:$E$718, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33554,7 +33574,7 @@
         <v>275</v>
       </c>
       <c r="N268" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B268, $C$2:$C$718, C268, $D$2:$D$718, D268, $E$2:$E$718, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33591,7 +33611,7 @@
       <c r="L269" s="18"/>
       <c r="M269" s="18"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B269, $C$2:$C$718, C269, $D$2:$D$718, D269, $E$2:$E$718, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O269" s="10"/>
@@ -33627,7 +33647,7 @@
       </c>
       <c r="J270" s="36"/>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B270, $C$2:$C$718, C270, $D$2:$D$718, D270, $E$2:$E$718, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33661,7 +33681,7 @@
       </c>
       <c r="J271" s="36"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B271, $C$2:$C$718, C271, $D$2:$D$718, D271, $E$2:$E$718, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33697,7 +33717,7 @@
         <v>118</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B272, $C$2:$C$718, C272, $D$2:$D$718, D272, $E$2:$E$718, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33743,7 +33763,7 @@
         <v>250</v>
       </c>
       <c r="N273" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B273, $C$2:$C$718, C273, $D$2:$D$718, D273, $E$2:$E$718, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P273" s="31"/>
@@ -33781,7 +33801,7 @@
       <c r="L274" s="18"/>
       <c r="M274" s="18"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B274, $C$2:$C$718, C274, $D$2:$D$718, D274, $E$2:$E$718, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O274" s="10"/>
@@ -33820,7 +33840,7 @@
       <c r="L275" s="18"/>
       <c r="M275" s="18"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B275, $C$2:$C$718, C275, $D$2:$D$718, D275, $E$2:$E$718, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O275" s="10"/>
@@ -33858,7 +33878,7 @@
         <v>118</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B276, $C$2:$C$718, C276, $D$2:$D$718, D276, $E$2:$E$718, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33894,7 +33914,7 @@
         <v>118</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B277, $C$2:$C$718, C277, $D$2:$D$718, D277, $E$2:$E$718, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33931,7 +33951,7 @@
       <c r="L278" s="18"/>
       <c r="M278" s="18"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B278, $C$2:$C$718, C278, $D$2:$D$718, D278, $E$2:$E$718, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O278" s="10"/>
@@ -33967,7 +33987,7 @@
       </c>
       <c r="J279" s="36"/>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B279, $C$2:$C$718, C279, $D$2:$D$718, D279, $E$2:$E$718, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O279" s="31"/>
@@ -34002,7 +34022,7 @@
       </c>
       <c r="J280" s="36"/>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B280, $C$2:$C$718, C280, $D$2:$D$718, D280, $E$2:$E$718, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34041,7 +34061,7 @@
       <c r="L281" s="18"/>
       <c r="M281" s="18"/>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B281, $C$2:$C$718, C281, $D$2:$D$718, D281, $E$2:$E$718, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O281" s="10"/>
@@ -34089,7 +34109,7 @@
         <v>300</v>
       </c>
       <c r="N282" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B282, $C$2:$C$718, C282, $D$2:$D$718, D282, $E$2:$E$718, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O282" s="10"/>
@@ -34125,7 +34145,7 @@
       </c>
       <c r="J283" s="36"/>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B283, $C$2:$C$718, C283, $D$2:$D$718, D283, $E$2:$E$718, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34161,7 +34181,7 @@
         <v>55</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B284, $C$2:$C$718, C284, $D$2:$D$718, D284, $E$2:$E$718, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34207,7 +34227,7 @@
         <v>250</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B285, $C$2:$C$718, C285, $D$2:$D$718, D285, $E$2:$E$718, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34243,7 +34263,7 @@
         <v>118</v>
       </c>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B286, $C$2:$C$718, C286, $D$2:$D$718, D286, $E$2:$E$718, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34277,7 +34297,7 @@
       </c>
       <c r="J287" s="36"/>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B287, $C$2:$C$718, C287, $D$2:$D$718, D287, $E$2:$E$718, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34316,7 +34336,7 @@
       <c r="L288" s="29"/>
       <c r="M288" s="29"/>
       <c r="N288" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B288, $C$2:$C$718, C288, $D$2:$D$718, D288, $E$2:$E$718, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O288" s="31"/>
@@ -34357,7 +34377,7 @@
       <c r="L289" s="29"/>
       <c r="M289" s="29"/>
       <c r="N289" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B289, $C$2:$C$718, C289, $D$2:$D$718, D289, $E$2:$E$718, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O289" s="31"/>
@@ -34395,7 +34415,7 @@
         <v>117</v>
       </c>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B290, $C$2:$C$718, C290, $D$2:$D$718, D290, $E$2:$E$718, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34433,7 +34453,7 @@
         <v>300</v>
       </c>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B291, $C$2:$C$718, C291, $D$2:$D$718, D291, $E$2:$E$718, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34467,11 +34487,11 @@
         <v>3430</v>
       </c>
       <c r="M292" s="18">
-        <f t="shared" ref="M292:M293" si="6">ABS((D292*E292)-L292)</f>
+        <f t="shared" ref="M292:M293" si="11">ABS((D292*E292)-L292)</f>
         <v>302</v>
       </c>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B292, $C$2:$C$718, C292, $D$2:$D$718, D292, $E$2:$E$718, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34505,11 +34525,11 @@
         <v>19950</v>
       </c>
       <c r="M293" s="18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="11"/>
         <v>650</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$718, B293, $C$2:$C$718, C293, $D$2:$D$718, D293, $E$2:$E$718, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
